--- a/VerveStacks_BIH_grids_kan10/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_BIH_grids_kan10/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -537,12 +537,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>e_Vogosca_BIH</t>
+          <t>e_Sarajevo_BIH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>grid node -- way/175002028-400 (Sarajevo, 8 km)</t>
+          <t>grid node -- BA17-220 (Sarajevo, 31 km)</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -560,19 +560,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>e_Prijedor_BIH</t>
+          <t>e_Tuzla_BIH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>grid node -- way/79818891-220 (Prijedor, 4 km)</t>
+          <t>grid node -- BA9-220 (Tuzla, 8 km)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -593,19 +593,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e_Tuzla_BIH</t>
+          <t>e_Prijedor_BIH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>grid node -- way/841600752-220 (Tuzla, 5 km)</t>
+          <t>grid node -- way/79818891-220 (Prijedor, 4 km)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -624,19 +624,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>e_Zenica_BIH</t>
+          <t>e_Mostar_BIH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>grid node -- BA11-220 (Zenica, 6 km)</t>
+          <t>grid node -- way/89827347-400 (Mostar, 5 km)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7"/>
